--- a/backend/uploads/qa_generated/SRS_-_FoodSmile_V2__1___1___2__a482d876.xlsx
+++ b/backend/uploads/qa_generated/SRS_-_FoodSmile_V2__1___1___2__a482d876.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,25 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Browallia New"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -60,8 +77,20 @@
         <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CDEEFF"/>
+        <bgColor rgb="00CDEEFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -83,11 +112,138 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+    </border>
+    <border/>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0C4DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0C4DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0C4DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0C4DE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,6 +263,60 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -473,205 +683,407 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SPECTRA QA PLATFORM - SRS_-_FoodSmile_V2__1___1_ (2) (Test Case)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="8" t="n"/>
+      <c r="L1" s="8" t="n"/>
+      <c r="M1" s="8" t="n"/>
+      <c r="N1" s="8" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="8" t="n"/>
+      <c r="N2" s="8" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="8" t="n"/>
+      <c r="N4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>Project Name :</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>FoodSmile (69-PUT)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>FoodSmile</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="n"/>
+      <c r="F6" s="31" t="n"/>
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>Create Date :</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Module / Function:</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>SRS_-_FoodSmile_V2__1___1_ (2)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Test Engine:</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Spectra AI (Gemini 3.1 Pro)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="2" t="inlineStr">
+      <c r="H6" s="27" t="n"/>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="J6" s="31" t="n"/>
+      <c r="K6" s="31" t="n"/>
+      <c r="L6" s="31" t="n"/>
+      <c r="M6" s="31" t="n"/>
+      <c r="N6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="18" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Project ID:</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Start Test Date :</t>
+        </is>
+      </c>
+      <c r="H8" s="27" t="n"/>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="J8" s="31" t="n"/>
+      <c r="K8" s="31" t="n"/>
+      <c r="L8" s="31" t="n"/>
+      <c r="M8" s="31" t="n"/>
+      <c r="N8" s="18" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TC-001</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
+      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="17" t="n"/>
+      <c r="M9" s="17" t="n"/>
+      <c r="N9" s="18" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Tester Name :</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Status :</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Baseline Specification</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Test ID</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Test Objective</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Test Description / Procedure</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Lead QA Architect</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="n"/>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Finish Test Date :</t>
+        </is>
+      </c>
+      <c r="H10" s="27" t="n"/>
+      <c r="I10" s="31" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="J10" s="31" t="n"/>
+      <c r="K10" s="31" t="n"/>
+      <c r="L10" s="31" t="n"/>
+      <c r="M10" s="31" t="n"/>
+      <c r="N10" s="18" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="17" t="n"/>
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="17" t="n"/>
+      <c r="L11" s="17" t="n"/>
+      <c r="M11" s="17" t="n"/>
+      <c r="N11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Project Release / Version :</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module / Function: </t>
+        </is>
+      </c>
+      <c r="H12" s="27" t="n"/>
+      <c r="I12" s="31" t="inlineStr">
+        <is>
+          <t>Test Cases</t>
+        </is>
+      </c>
+      <c r="J12" s="31" t="n"/>
+      <c r="K12" s="31" t="n"/>
+      <c r="L12" s="31" t="n"/>
+      <c r="M12" s="31" t="n"/>
+      <c r="N12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="25" t="n"/>
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="25" t="n"/>
+      <c r="L13" s="25" t="n"/>
+      <c r="M13" s="25" t="n"/>
+      <c r="N13" s="26" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> FUNCTIONAL REQUIREMENTS (Requirements No.) :</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>REQ0001-REQ0050</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="32" customHeight="1">
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Test Case Objective</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>Test Step</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
+        <is>
+          <t>Test Type</t>
+        </is>
+      </c>
+      <c r="G17" s="29" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="H17" s="29" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I17" s="29" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J17" s="29" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+      <c r="K17" s="29" t="inlineStr">
+        <is>
+          <t>Automate</t>
+        </is>
+      </c>
+      <c r="L17" s="29" t="inlineStr">
         <is>
           <t>Req No.</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="M17" s="29" t="inlineStr">
+        <is>
+          <t>Platforms</t>
+        </is>
+      </c>
+      <c r="N17" s="29" t="inlineStr">
         <is>
           <t>Updated By</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>TC-001</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Verify SRS_-_FoodSmile_V2__1___1_ (2) functionality</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>1. Execute test steps as per requirements.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Default test parameters</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>System behaves as expected.</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Working properly</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>REQ-01</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>AI Agent</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="20">
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I12:M12"/>
+    <mergeCell ref="B1:N4"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="D10:F10"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="I10:M10"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
